--- a/jogos_2025-11-02.xlsx
+++ b/jogos_2025-11-02.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chaves II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Chaves II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7551,10 +7551,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Negeri Sembilan</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,22 +9534,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Negeri Sembilan</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9873,10 +9873,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10002,10 +10002,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10131,10 +10131,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.45</v>
+        <v>2.5</v>
       </c>
       <c r="M76" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="N76" t="n">
-        <v>7.3</v>
+        <v>2.65</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,16 +10254,16 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10389,10 +10389,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,22 +11082,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,16 +13350,16 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,16 +13479,16 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>10.01</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -17865,10 +17865,10 @@
         <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA135" t="n">
         <v>0</v>
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18471,13 +18471,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>5.94</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18510,10 +18510,10 @@
         <v>0</v>
       </c>
       <c r="Y140" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z140" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA140" t="n">
         <v>0</v>
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18729,13 +18729,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>7.86</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -18768,10 +18768,10 @@
         <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z142" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA142" t="n">
         <v>0</v>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19116,13 +19116,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -19155,10 +19155,10 @@
         <v>0</v>
       </c>
       <c r="Y145" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z145" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA145" t="n">
         <v>0</v>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19245,13 +19245,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>2.86</v>
+        <v>2</v>
       </c>
       <c r="M146" t="n">
-        <v>3.04</v>
+        <v>3.8</v>
       </c>
       <c r="N146" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -19284,10 +19284,10 @@
         <v>0</v>
       </c>
       <c r="Y146" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z146" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA146" t="n">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19503,13 +19503,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -19542,10 +19542,10 @@
         <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z148" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA148" t="n">
         <v>0</v>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20019,13 +20019,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -20058,10 +20058,10 @@
         <v>0</v>
       </c>
       <c r="Y152" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z152" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA152" t="n">
         <v>0</v>
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20148,13 +20148,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -20187,10 +20187,10 @@
         <v>0</v>
       </c>
       <c r="Y153" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z153" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA153" t="n">
         <v>0</v>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,22 +20886,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21567,13 +21567,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -21606,10 +21606,10 @@
         <v>0</v>
       </c>
       <c r="Y164" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z164" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA164" t="n">
         <v>0</v>
@@ -21660,7 +21660,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21696,13 +21696,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>7.86</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -21735,10 +21735,10 @@
         <v>0</v>
       </c>
       <c r="Y165" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z165" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA165" t="n">
         <v>0</v>
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>AD Marco 09</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22305,22 +22305,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22470,13 +22470,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -22509,10 +22509,10 @@
         <v>0</v>
       </c>
       <c r="Y171" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z171" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA171" t="n">
         <v>0</v>
@@ -22563,7 +22563,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>AD Marco 09</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23079,22 +23079,22 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23115,13 +23115,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -23154,10 +23154,10 @@
         <v>0</v>
       </c>
       <c r="Y176" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z176" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA176" t="n">
         <v>0</v>
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23502,13 +23502,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -23595,22 +23595,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23760,13 +23760,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>10.01</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -23799,10 +23799,10 @@
         <v>0</v>
       </c>
       <c r="Y181" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA181" t="n">
         <v>0</v>
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23889,13 +23889,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -23928,10 +23928,10 @@
         <v>0</v>
       </c>
       <c r="Y182" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z182" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA182" t="n">
         <v>0</v>
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24663,13 +24663,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -24702,10 +24702,10 @@
         <v>0</v>
       </c>
       <c r="Y188" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z188" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA188" t="n">
         <v>0</v>
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -24921,13 +24921,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M190" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -24960,10 +24960,10 @@
         <v>0</v>
       </c>
       <c r="Y190" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z190" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA190" t="n">
         <v>0</v>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25050,13 +25050,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M191" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -25089,10 +25089,10 @@
         <v>0</v>
       </c>
       <c r="Y191" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z191" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA191" t="n">
         <v>0</v>
@@ -25143,22 +25143,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25437,13 +25437,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>5.94</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -25476,10 +25476,10 @@
         <v>0</v>
       </c>
       <c r="Y194" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z194" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA194" t="n">
         <v>0</v>
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25566,13 +25566,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -25605,10 +25605,10 @@
         <v>0</v>
       </c>
       <c r="Y195" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z195" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA195" t="n">
         <v>0</v>
@@ -25659,22 +25659,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25824,13 +25824,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -25863,10 +25863,10 @@
         <v>0</v>
       </c>
       <c r="Y197" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z197" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA197" t="n">
         <v>0</v>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26562,22 +26562,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,22 +26691,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27243,13 +27243,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M208" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -27282,10 +27282,10 @@
         <v>0</v>
       </c>
       <c r="Y208" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z208" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA208" t="n">
         <v>0</v>
@@ -27336,7 +27336,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27372,13 +27372,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N209" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -27411,10 +27411,10 @@
         <v>0</v>
       </c>
       <c r="Y209" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z209" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA209" t="n">
         <v>0</v>
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28239,7 +28239,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28626,7 +28626,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29400,22 +29400,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30045,22 +30045,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30432,22 +30432,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30690,7 +30690,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30819,22 +30819,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31464,22 +31464,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31722,7 +31722,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -31861,12 +31861,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32109,22 +32109,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32238,7 +32238,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -32377,12 +32377,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32496,7 +32496,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32625,7 +32625,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32661,13 +32661,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M250" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32790,13 +32790,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M251" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -32829,10 +32829,10 @@
         <v>0</v>
       </c>
       <c r="Y251" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z251" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA251" t="n">
         <v>0</v>
@@ -32893,12 +32893,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -32919,13 +32919,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M252" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N252" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -32958,10 +32958,10 @@
         <v>0</v>
       </c>
       <c r="Y252" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z252" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA252" t="n">
         <v>0</v>
@@ -33022,12 +33022,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33048,13 +33048,13 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M253" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N253" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O253" t="n">
         <v>0</v>
@@ -33151,12 +33151,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33786,7 +33786,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34044,7 +34044,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -34054,12 +34054,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34818,7 +34818,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -34828,12 +34828,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34854,13 +34854,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N267" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -34899,10 +34899,10 @@
         <v>0</v>
       </c>
       <c r="AA267" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB267" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC267" t="n">
         <v>0</v>
@@ -34947,7 +34947,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -34957,12 +34957,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -35205,7 +35205,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -35215,12 +35215,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35334,7 +35334,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -35344,12 +35344,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35463,7 +35463,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -35473,12 +35473,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35592,7 +35592,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -35602,12 +35602,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -35628,13 +35628,13 @@
         </is>
       </c>
       <c r="L273" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N273" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O273" t="n">
         <v>0</v>
@@ -35673,10 +35673,10 @@
         <v>0</v>
       </c>
       <c r="AA273" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB273" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC273" t="n">
         <v>0</v>
@@ -35731,12 +35731,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -35860,12 +35860,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -35989,12 +35989,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36108,7 +36108,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -36118,12 +36118,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Royal Antwerp FC</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -36144,13 +36144,13 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N277" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
@@ -36183,10 +36183,10 @@
         <v>0</v>
       </c>
       <c r="Y277" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z277" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -36237,7 +36237,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -36247,12 +36247,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36273,13 +36273,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N278" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -36312,10 +36312,10 @@
         <v>0</v>
       </c>
       <c r="Y278" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z278" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA278" t="n">
         <v>0</v>
@@ -36366,7 +36366,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -36376,12 +36376,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Royal Antwerp FC</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36402,13 +36402,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>1.88</v>
+        <v>12</v>
       </c>
       <c r="M279" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="N279" t="n">
-        <v>3.85</v>
+        <v>1.23</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -36444,7 +36444,7 @@
         <v>1.7</v>
       </c>
       <c r="Z279" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AA279" t="n">
         <v>0</v>
@@ -36495,7 +36495,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -36505,12 +36505,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -36624,22 +36624,22 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -36882,7 +36882,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -36892,12 +36892,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -37011,22 +37011,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37140,7 +37140,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -37150,12 +37150,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -37279,12 +37279,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -37656,7 +37656,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -37666,12 +37666,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -37785,7 +37785,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -37795,12 +37795,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -38172,22 +38172,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -38208,13 +38208,13 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>1.18</v>
+        <v>1.8</v>
       </c>
       <c r="M293" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="N293" t="n">
-        <v>13</v>
+        <v>4.7</v>
       </c>
       <c r="O293" t="n">
         <v>0</v>
@@ -38241,16 +38241,16 @@
         <v>0</v>
       </c>
       <c r="W293" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X293" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y293" t="n">
-        <v>1.71</v>
+        <v>2.45</v>
       </c>
       <c r="Z293" t="n">
-        <v>2.01</v>
+        <v>1.5</v>
       </c>
       <c r="AA293" t="n">
         <v>0</v>
@@ -38301,7 +38301,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -38311,12 +38311,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -38337,13 +38337,13 @@
         </is>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M294" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N294" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O294" t="n">
         <v>0</v>
@@ -38376,10 +38376,10 @@
         <v>0</v>
       </c>
       <c r="Y294" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z294" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA294" t="n">
         <v>0</v>
@@ -38430,22 +38430,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -38466,13 +38466,13 @@
         </is>
       </c>
       <c r="L295" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="M295" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="N295" t="n">
-        <v>2.8</v>
+        <v>2.03</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -38505,16 +38505,16 @@
         <v>0</v>
       </c>
       <c r="Y295" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z295" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA295" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB295" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC295" t="n">
         <v>0</v>
@@ -38559,22 +38559,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -38595,13 +38595,13 @@
         </is>
       </c>
       <c r="L296" t="n">
-        <v>1.8</v>
+        <v>1.18</v>
       </c>
       <c r="M296" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="N296" t="n">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="O296" t="n">
         <v>0</v>
@@ -38628,16 +38628,16 @@
         <v>0</v>
       </c>
       <c r="W296" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X296" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y296" t="n">
-        <v>2.45</v>
+        <v>1.71</v>
       </c>
       <c r="Z296" t="n">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="AA296" t="n">
         <v>0</v>
@@ -38688,22 +38688,22 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -38724,13 +38724,13 @@
         </is>
       </c>
       <c r="L297" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M297" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N297" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O297" t="n">
         <v>0</v>
@@ -38769,10 +38769,10 @@
         <v>0</v>
       </c>
       <c r="AA297" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB297" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC297" t="n">
         <v>0</v>
@@ -38817,7 +38817,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -38827,12 +38827,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -38946,7 +38946,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -38956,12 +38956,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -39075,7 +39075,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -39085,12 +39085,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -39204,7 +39204,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -39214,12 +39214,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -39333,7 +39333,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -39343,12 +39343,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -39369,13 +39369,13 @@
         </is>
       </c>
       <c r="L302" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M302" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N302" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O302" t="n">
         <v>0</v>
@@ -39408,10 +39408,10 @@
         <v>0</v>
       </c>
       <c r="Y302" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z302" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA302" t="n">
         <v>0</v>
@@ -39462,7 +39462,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -39472,12 +39472,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -39730,12 +39730,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -39849,22 +39849,22 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -39978,22 +39978,22 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -40117,12 +40117,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -40246,12 +40246,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -40494,7 +40494,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -40504,12 +40504,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -40633,12 +40633,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -40762,12 +40762,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -40891,12 +40891,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -40917,13 +40917,13 @@
         </is>
       </c>
       <c r="L314" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M314" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N314" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O314" t="n">
         <v>0</v>
@@ -40956,10 +40956,10 @@
         <v>0</v>
       </c>
       <c r="Y314" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z314" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA314" t="n">
         <v>0</v>
@@ -41010,7 +41010,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -41020,12 +41020,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -41046,13 +41046,13 @@
         </is>
       </c>
       <c r="L315" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M315" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N315" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O315" t="n">
         <v>0</v>
@@ -41085,10 +41085,10 @@
         <v>0</v>
       </c>
       <c r="Y315" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z315" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA315" t="n">
         <v>0</v>
@@ -41278,12 +41278,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -41407,12 +41407,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -41536,12 +41536,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -41665,12 +41665,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -41794,12 +41794,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -41923,12 +41923,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -42042,7 +42042,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -42052,12 +42052,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G323" t="n">
@@ -42300,7 +42300,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -42310,12 +42310,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -42429,7 +42429,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -42439,12 +42439,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G326" t="n">
